--- a/data/trans_bre/P16A13-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A13-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,33</t>
+          <t>0,48; 3,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,66</t>
+          <t>-2,48; 2,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,27</t>
+          <t>-1,08; 3,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 5,27</t>
+          <t>-0,9; 5,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,41; 555,77</t>
+          <t>16,57; 608,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 85,41</t>
+          <t>-39,79; 79,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 124,27</t>
+          <t>-24,17; 116,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 64,69</t>
+          <t>-7,14; 68,7</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,56</t>
+          <t>-1,62; 1,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,35</t>
+          <t>-0,45; 3,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,1</t>
+          <t>-1,08; 2,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,53</t>
+          <t>2,81; 7,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 69,17</t>
+          <t>-41,33; 65,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 111,99</t>
+          <t>-10,31; 112,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 102,81</t>
+          <t>-31,66; 102,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,78; 331,85</t>
+          <t>51,72; 325,67</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,9</t>
+          <t>-1,09; 2,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,26</t>
+          <t>-0,97; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,09</t>
+          <t>-1,01; 3,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,35</t>
+          <t>-3,75; 1,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 107,16</t>
+          <t>-25,49; 99,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,84; 130,2</t>
+          <t>-22,34; 117,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 158,73</t>
+          <t>-27,91; 150,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 33,44</t>
+          <t>-61,37; 28,53</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 3,01</t>
+          <t>-0,17; 3,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,93</t>
+          <t>-0,56; 3,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,6</t>
+          <t>0,07; 3,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,4</t>
+          <t>-1,91; 2,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 168,88</t>
+          <t>-8,44; 163,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 113,41</t>
+          <t>-9,76; 112,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 190,01</t>
+          <t>0,28; 196,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 40,85</t>
+          <t>-22,74; 42,88</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,77</t>
+          <t>0,08; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,34</t>
+          <t>0,2; 2,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,07</t>
+          <t>0,18; 1,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,27</t>
+          <t>0,16; 3,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 78,22</t>
+          <t>1,76; 85,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 64,62</t>
+          <t>4,07; 66,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 80,53</t>
+          <t>4,94; 77,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 62,71</t>
+          <t>3,32; 67,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A13-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A13-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,44</t>
+          <t>0,4; 3,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,57</t>
+          <t>-2,35; 2,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,25</t>
+          <t>-1,03; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,45</t>
+          <t>0,48; 5,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,57; 608,99</t>
+          <t>7,78; 523,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 79,76</t>
+          <t>-41,27; 75,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 116,94</t>
+          <t>-23,14; 129,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 68,7</t>
+          <t>4,35; 77,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>117,97%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,51</t>
+          <t>-1,64; 1,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,65</t>
+          <t>-0,72; 3,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,2</t>
+          <t>-1,11; 2,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,34</t>
+          <t>1,63; 5,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,33; 65,17</t>
+          <t>-41,74; 64,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 112,91</t>
+          <t>-15,52; 107,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 102,15</t>
+          <t>-30,46; 113,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,72; 325,67</t>
+          <t>26,91; 130,0</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-16,58%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,81</t>
+          <t>-1,09; 3,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,44</t>
+          <t>-0,75; 3,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,03</t>
+          <t>-0,92; 3,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,3</t>
+          <t>-1,66; 2,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,49; 99,98</t>
+          <t>-25,97; 117,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 117,02</t>
+          <t>-17,02; 135,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 150,77</t>
+          <t>-24,48; 165,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 28,53</t>
+          <t>-27,03; 62,26</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,04</t>
+          <t>-0,08; 2,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,92</t>
+          <t>-0,29; 3,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,47</t>
+          <t>-0,02; 3,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,38</t>
+          <t>-0,81; 2,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 163,75</t>
+          <t>-4,12; 178,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 112,76</t>
+          <t>-5,13; 115,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 196,58</t>
+          <t>-1,99; 187,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 42,88</t>
+          <t>-10,39; 50,55</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,82</t>
+          <t>0,08; 1,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,36</t>
+          <t>0,18; 2,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,95</t>
+          <t>0,22; 2,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,36</t>
+          <t>1,01; 3,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 85,31</t>
+          <t>1,07; 74,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 66,76</t>
+          <t>3,62; 60,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 77,86</t>
+          <t>6,52; 85,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 67,03</t>
+          <t>15,02; 54,54</t>
         </is>
       </c>
     </row>
